--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -991,7 +991,7 @@
     <t>0.9648,0.0167,0.0117,0.0006</t>
   </si>
   <si>
-    <t>0.9770,0.0014,0.0133,0.0004</t>
+    <t>0.9770,0.0014,0.0132,0.0004</t>
   </si>
   <si>
     <t>0.9726,0.0143,0.0056,0.0020</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="528">
   <si>
     <t>Filename</t>
   </si>
@@ -820,28 +820,37 @@
     <t>0,1,0,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,1,0</t>
   </si>
   <si>
     <t>0,1,0,1</t>
   </si>
   <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0.9630,0.0037,0.0090,0.0015</t>
   </si>
   <si>
     <t>0.0060,0.0033,0.0001,0.9982</t>
   </si>
   <si>
-    <t>0.9087,0.0023,0.0004,0.0312</t>
-  </si>
-  <si>
-    <t>0.2550,0.0008,0.0014,0.7291</t>
+    <t>0.9084,0.0023,0.0004,0.0313</t>
+  </si>
+  <si>
+    <t>0.2547,0.0008,0.0014,0.7294</t>
   </si>
   <si>
     <t>0.9894,0.0031,0.0020,0.0007</t>
   </si>
   <si>
-    <t>0.9859,0.0086,0.0014,0.0010</t>
+    <t>0.9859,0.0087,0.0014,0.0010</t>
   </si>
   <si>
     <t>0.9848,0.0029,0.0045,0.0007</t>
@@ -859,31 +868,31 @@
     <t>0.9938,0.0017,0.0010,0.0003</t>
   </si>
   <si>
-    <t>0.9905,0.0022,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.8178,0.0070,0.1552,0.0016</t>
-  </si>
-  <si>
-    <t>0.0152,0.0545,0.9532,0.0028</t>
-  </si>
-  <si>
-    <t>0.1549,0.0010,0.9023,0.0003</t>
-  </si>
-  <si>
-    <t>0.0664,0.0054,0.9423,0.0016</t>
-  </si>
-  <si>
-    <t>0.4794,0.0014,0.5979,0.0004</t>
+    <t>0.9905,0.0023,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.8177,0.0070,0.1553,0.0016</t>
+  </si>
+  <si>
+    <t>0.0152,0.0542,0.9533,0.0028</t>
+  </si>
+  <si>
+    <t>0.1549,0.0010,0.9024,0.0003</t>
+  </si>
+  <si>
+    <t>0.0663,0.0054,0.9424,0.0016</t>
+  </si>
+  <si>
+    <t>0.4796,0.0014,0.5977,0.0004</t>
   </si>
   <si>
     <t>0.0010,0.9988,0.0094,0.0002</t>
   </si>
   <si>
-    <t>0.0017,0.9971,0.0041,0.0016</t>
-  </si>
-  <si>
-    <t>0.2622,0.8953,0.0023,0.0000</t>
+    <t>0.0017,0.9970,0.0041,0.0016</t>
+  </si>
+  <si>
+    <t>0.2621,0.8953,0.0023,0.0000</t>
   </si>
   <si>
     <t>0.0027,0.9948,0.0097,0.0038</t>
@@ -892,10 +901,10 @@
     <t>0.0014,0.9991,0.0391,0.0000</t>
   </si>
   <si>
-    <t>0.5876,0.0005,0.5172,0.0006</t>
-  </si>
-  <si>
-    <t>0.0867,0.0086,0.9209,0.0064</t>
+    <t>0.5875,0.0005,0.5174,0.0006</t>
+  </si>
+  <si>
+    <t>0.0867,0.0086,0.9210,0.0064</t>
   </si>
   <si>
     <t>0.0241,0.0002,0.9890,0.0001</t>
@@ -907,13 +916,13 @@
     <t>0.0200,0.0010,0.9865,0.0007</t>
   </si>
   <si>
-    <t>0.0860,0.0006,0.9496,0.0004</t>
-  </si>
-  <si>
-    <t>0.0117,0.0005,0.9916,0.0005</t>
-  </si>
-  <si>
-    <t>0.6267,0.4244,0.0408,0.0015</t>
+    <t>0.0861,0.0006,0.9496,0.0004</t>
+  </si>
+  <si>
+    <t>0.0117,0.0005,0.9917,0.0005</t>
+  </si>
+  <si>
+    <t>0.6272,0.4238,0.0408,0.0015</t>
   </si>
   <si>
     <t>0.9522,0.0474,0.0055,0.0012</t>
@@ -922,19 +931,19 @@
     <t>0.0015,0.0001,0.9985,0.0002</t>
   </si>
   <si>
-    <t>0.0117,0.3488,0.8656,0.0015</t>
-  </si>
-  <si>
-    <t>0.9305,0.0016,0.0508,0.0007</t>
-  </si>
-  <si>
-    <t>0.8426,0.0067,0.1223,0.0017</t>
-  </si>
-  <si>
-    <t>0.2900,0.8462,0.0159,0.0009</t>
-  </si>
-  <si>
-    <t>0.0132,0.9651,0.4316,0.0039</t>
+    <t>0.0117,0.3477,0.8659,0.0015</t>
+  </si>
+  <si>
+    <t>0.9304,0.0016,0.0509,0.0007</t>
+  </si>
+  <si>
+    <t>0.8425,0.0067,0.1224,0.0017</t>
+  </si>
+  <si>
+    <t>0.2902,0.8461,0.0159,0.0009</t>
+  </si>
+  <si>
+    <t>0.0132,0.9651,0.4315,0.0039</t>
   </si>
   <si>
     <t>0.0005,0.9067,0.9572,0.0002</t>
@@ -943,13 +952,13 @@
     <t>0.0009,0.0035,0.9967,0.0039</t>
   </si>
   <si>
-    <t>0.0339,0.0224,0.9444,0.0122</t>
-  </si>
-  <si>
-    <t>0.0716,0.0005,0.8743,0.0513</t>
-  </si>
-  <si>
-    <t>0.0009,0.9423,0.8156,0.0008</t>
+    <t>0.0339,0.0223,0.9444,0.0122</t>
+  </si>
+  <si>
+    <t>0.0715,0.0005,0.8745,0.0512</t>
+  </si>
+  <si>
+    <t>0.0009,0.9422,0.8157,0.0008</t>
   </si>
   <si>
     <t>0.0004,0.9964,0.0072,0.0010</t>
@@ -958,7 +967,7 @@
     <t>0.0051,0.0126,0.9893,0.0017</t>
   </si>
   <si>
-    <t>0.0007,0.6197,0.0014,0.9742</t>
+    <t>0.0007,0.6196,0.0014,0.9742</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0002,0.0001</t>
@@ -973,13 +982,13 @@
     <t>0.0011,0.0204,0.9923,0.0021</t>
   </si>
   <si>
-    <t>0.0008,0.1233,0.9908,0.0016</t>
+    <t>0.0008,0.1232,0.9908,0.0016</t>
   </si>
   <si>
     <t>0.0113,0.0020,0.9876,0.0011</t>
   </si>
   <si>
-    <t>0.0394,0.0001,0.9858,0.0000</t>
+    <t>0.0395,0.0001,0.9858,0.0000</t>
   </si>
   <si>
     <t>0.0187,0.0016,0.9853,0.0005</t>
@@ -991,31 +1000,31 @@
     <t>0.9648,0.0167,0.0117,0.0006</t>
   </si>
   <si>
-    <t>0.9770,0.0014,0.0132,0.0004</t>
+    <t>0.9770,0.0014,0.0133,0.0004</t>
   </si>
   <si>
     <t>0.9726,0.0143,0.0056,0.0020</t>
   </si>
   <si>
-    <t>0.2629,0.0007,0.7827,0.0008</t>
-  </si>
-  <si>
-    <t>0.9774,0.0011,0.0129,0.0005</t>
-  </si>
-  <si>
-    <t>0.9856,0.0028,0.0048,0.0008</t>
+    <t>0.2623,0.0007,0.7835,0.0008</t>
+  </si>
+  <si>
+    <t>0.9774,0.0011,0.0130,0.0005</t>
+  </si>
+  <si>
+    <t>0.9856,0.0028,0.0049,0.0008</t>
   </si>
   <si>
     <t>0.9830,0.0014,0.0078,0.0003</t>
   </si>
   <si>
-    <t>0.0001,0.9981,0.8941,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0141,0.9976,0.0002</t>
-  </si>
-  <si>
-    <t>0.0039,0.0363,0.9896,0.0022</t>
+    <t>0.0001,0.9981,0.8942,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0140,0.9976,0.0002</t>
+  </si>
+  <si>
+    <t>0.0039,0.0362,0.9896,0.0022</t>
   </si>
   <si>
     <t>0.0002,0.9749,0.9568,0.0003</t>
@@ -1030,19 +1039,19 @@
     <t>0.0003,0.9993,0.0046,0.0000</t>
   </si>
   <si>
-    <t>0.9633,0.0017,0.0257,0.0003</t>
-  </si>
-  <si>
-    <t>0.2182,0.1859,0.5370,0.0041</t>
+    <t>0.9632,0.0017,0.0258,0.0003</t>
+  </si>
+  <si>
+    <t>0.2183,0.1853,0.5374,0.0041</t>
   </si>
   <si>
     <t>0.0069,0.0056,0.9896,0.0012</t>
   </si>
   <si>
-    <t>0.0002,0.9766,0.9574,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9538,0.9718,0.0001</t>
+    <t>0.0002,0.9765,0.9574,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9537,0.9718,0.0001</t>
   </si>
   <si>
     <t>0.0001,0.9989,0.3983,0.0000</t>
@@ -1069,31 +1078,31 @@
     <t>0.0002,0.0010,0.0009,0.9999</t>
   </si>
   <si>
-    <t>0.0003,0.9972,0.5578,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9140,0.9744,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.9720,0.7903,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.8952,0.9888,0.0001</t>
+    <t>0.0003,0.9972,0.5584,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9138,0.9744,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.9720,0.7906,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.8950,0.9888,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9941,0.9727,0.0000</t>
   </si>
   <si>
-    <t>0.0006,0.9907,0.4734,0.0003</t>
+    <t>0.0006,0.9907,0.4736,0.0003</t>
   </si>
   <si>
     <t>0.9908,0.0074,0.0007,0.0004</t>
   </si>
   <si>
-    <t>0.9596,0.0236,0.0076,0.0015</t>
-  </si>
-  <si>
-    <t>0.9633,0.0481,0.0016,0.0005</t>
+    <t>0.9595,0.0236,0.0076,0.0015</t>
+  </si>
+  <si>
+    <t>0.9632,0.0481,0.0016,0.0005</t>
   </si>
   <si>
     <t>0.9916,0.0052,0.0012,0.0004</t>
@@ -1105,7 +1114,7 @@
     <t>0.9882,0.0069,0.0018,0.0020</t>
   </si>
   <si>
-    <t>0.9511,0.0054,0.0251,0.0019</t>
+    <t>0.9510,0.0054,0.0252,0.0019</t>
   </si>
   <si>
     <t>0.9779,0.0022,0.0041,0.0005</t>
@@ -1120,10 +1129,10 @@
     <t>0.9930,0.0021,0.0011,0.0006</t>
   </si>
   <si>
-    <t>0.9921,0.0038,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.9753,0.0114,0.0043,0.0037</t>
+    <t>0.9920,0.0038,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9752,0.0114,0.0043,0.0037</t>
   </si>
   <si>
     <t>0.9948,0.0026,0.0007,0.0009</t>
@@ -1138,13 +1147,13 @@
     <t>0.0009,0.0001,0.9993,0.0000</t>
   </si>
   <si>
-    <t>0.0526,0.0029,0.9599,0.0016</t>
-  </si>
-  <si>
-    <t>0.9683,0.0001,0.0430,0.0000</t>
-  </si>
-  <si>
-    <t>0.0567,0.0011,0.9640,0.0006</t>
+    <t>0.0526,0.0029,0.9600,0.0016</t>
+  </si>
+  <si>
+    <t>0.9682,0.0001,0.0431,0.0000</t>
+  </si>
+  <si>
+    <t>0.0568,0.0011,0.9639,0.0006</t>
   </si>
   <si>
     <t>0.0002,0.9997,0.0006,0.0001</t>
@@ -1153,10 +1162,10 @@
     <t>0.0002,0.9998,0.0011,0.0000</t>
   </si>
   <si>
-    <t>0.6349,0.5260,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.2024,0.8798,0.0117,0.0015</t>
+    <t>0.6351,0.5256,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.2030,0.8794,0.0117,0.0015</t>
   </si>
   <si>
     <t>0.0004,0.9996,0.0009,0.0001</t>
@@ -1165,22 +1174,22 @@
     <t>0.0000,0.9999,0.0004,0.0000</t>
   </si>
   <si>
-    <t>0.9065,0.1624,0.0074,0.0005</t>
-  </si>
-  <si>
-    <t>0.1857,0.0189,0.8078,0.0067</t>
+    <t>0.9067,0.1621,0.0074,0.0005</t>
+  </si>
+  <si>
+    <t>0.1855,0.0189,0.8081,0.0066</t>
   </si>
   <si>
     <t>0.0827,0.0071,0.9190,0.0065</t>
   </si>
   <si>
-    <t>0.4991,0.0071,0.5154,0.0015</t>
-  </si>
-  <si>
-    <t>0.2037,0.0109,0.8220,0.0074</t>
-  </si>
-  <si>
-    <t>0.0009,0.6751,0.8854,0.0650</t>
+    <t>0.4989,0.0071,0.5157,0.0015</t>
+  </si>
+  <si>
+    <t>0.2039,0.0109,0.8219,0.0074</t>
+  </si>
+  <si>
+    <t>0.0009,0.6742,0.8855,0.0652</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0023,0.0000</t>
@@ -1189,19 +1198,19 @@
     <t>0.0000,0.9999,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9986,0.0007,0.0153</t>
+    <t>0.0001,0.9986,0.0007,0.0154</t>
   </si>
   <si>
     <t>0.0001,0.9986,0.0164,0.0006</t>
   </si>
   <si>
-    <t>0.0018,0.9970,0.2155,0.0002</t>
-  </si>
-  <si>
-    <t>0.2796,0.7288,0.1000,0.0038</t>
-  </si>
-  <si>
-    <t>0.0316,0.9615,0.0457,0.0101</t>
+    <t>0.0018,0.9970,0.2158,0.0002</t>
+  </si>
+  <si>
+    <t>0.2801,0.7283,0.0999,0.0038</t>
+  </si>
+  <si>
+    <t>0.0316,0.9615,0.0458,0.0101</t>
   </si>
   <si>
     <t>0.9944,0.0005,0.0013,0.0003</t>
@@ -1219,19 +1228,19 @@
     <t>0.9934,0.0034,0.0010,0.0011</t>
   </si>
   <si>
-    <t>0.9607,0.0009,0.0121,0.0029</t>
+    <t>0.9606,0.0009,0.0121,0.0029</t>
   </si>
   <si>
     <t>0.9888,0.0019,0.0028,0.0013</t>
   </si>
   <si>
-    <t>0.9911,0.0009,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.9611,0.9256,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.6520,0.9944,0.0000</t>
+    <t>0.9910,0.0009,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.9610,0.9256,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.6515,0.9944,0.0000</t>
   </si>
   <si>
     <t>0.0004,0.0266,0.9982,0.0006</t>
@@ -1243,13 +1252,13 @@
     <t>0.9586,0.0015,0.0321,0.0002</t>
   </si>
   <si>
-    <t>0.3628,0.3358,0.1579,0.0091</t>
-  </si>
-  <si>
-    <t>0.1758,0.0006,0.8818,0.0014</t>
-  </si>
-  <si>
-    <t>0.6843,0.0076,0.2938,0.0028</t>
+    <t>0.3634,0.3347,0.1584,0.0091</t>
+  </si>
+  <si>
+    <t>0.1760,0.0006,0.8817,0.0014</t>
+  </si>
+  <si>
+    <t>0.6840,0.0075,0.2944,0.0028</t>
   </si>
   <si>
     <t>0.0035,0.0001,0.0007,0.9994</t>
@@ -1267,7 +1276,7 @@
     <t>0.0002,0.9899,0.8961,0.0001</t>
   </si>
   <si>
-    <t>0.9755,0.0011,0.0125,0.0008</t>
+    <t>0.9755,0.0011,0.0126,0.0008</t>
   </si>
   <si>
     <t>0.0211,0.9752,0.0156,0.0064</t>
@@ -1282,22 +1291,22 @@
     <t>0.9895,0.0019,0.0014,0.0010</t>
   </si>
   <si>
-    <t>0.0985,0.0000,0.9627,0.0000</t>
-  </si>
-  <si>
-    <t>0.0716,0.0001,0.9592,0.0000</t>
+    <t>0.0981,0.0000,0.9628,0.0000</t>
+  </si>
+  <si>
+    <t>0.0715,0.0001,0.9593,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.8482,0.0004,0.0970,0.0066</t>
+    <t>0.8478,0.0004,0.0974,0.0067</t>
   </si>
   <si>
     <t>0.9501,0.0067,0.0136,0.0036</t>
   </si>
   <si>
-    <t>0.5891,0.2412,0.0599,0.0017</t>
+    <t>0.5890,0.2411,0.0600,0.0017</t>
   </si>
   <si>
     <t>0.9866,0.0013,0.0053,0.0002</t>
@@ -1306,13 +1315,13 @@
     <t>0.9273,0.0469,0.0142,0.0034</t>
   </si>
   <si>
-    <t>0.1079,0.8843,0.0545,0.0108</t>
-  </si>
-  <si>
-    <t>0.9227,0.0108,0.0479,0.0007</t>
-  </si>
-  <si>
-    <t>0.7965,0.0372,0.1277,0.0026</t>
+    <t>0.1079,0.8842,0.0545,0.0108</t>
+  </si>
+  <si>
+    <t>0.9225,0.0108,0.0481,0.0007</t>
+  </si>
+  <si>
+    <t>0.7963,0.0372,0.1280,0.0026</t>
   </si>
   <si>
     <t>0.9929,0.0022,0.0013,0.0003</t>
@@ -1324,7 +1333,7 @@
     <t>0.9826,0.0041,0.0050,0.0009</t>
   </si>
   <si>
-    <t>0.9882,0.0007,0.0046,0.0004</t>
+    <t>0.9881,0.0007,0.0046,0.0004</t>
   </si>
   <si>
     <t>0.9907,0.0031,0.0017,0.0003</t>
@@ -1339,34 +1348,34 @@
     <t>0.9900,0.0010,0.0029,0.0005</t>
   </si>
   <si>
-    <t>0.6511,0.4515,0.0124,0.0020</t>
-  </si>
-  <si>
-    <t>0.4780,0.6442,0.0122,0.0024</t>
-  </si>
-  <si>
-    <t>0.7652,0.2707,0.0070,0.0018</t>
-  </si>
-  <si>
-    <t>0.7097,0.0382,0.1871,0.0013</t>
+    <t>0.6514,0.4511,0.0124,0.0020</t>
+  </si>
+  <si>
+    <t>0.4783,0.6438,0.0122,0.0024</t>
+  </si>
+  <si>
+    <t>0.7648,0.2709,0.0070,0.0018</t>
+  </si>
+  <si>
+    <t>0.7092,0.0382,0.1877,0.0013</t>
   </si>
   <si>
     <t>0.9876,0.0069,0.0021,0.0003</t>
   </si>
   <si>
-    <t>0.5517,0.3311,0.0691,0.0014</t>
-  </si>
-  <si>
-    <t>0.9846,0.0025,0.0048,0.0003</t>
-  </si>
-  <si>
-    <t>0.9649,0.0260,0.0078,0.0013</t>
+    <t>0.5518,0.3308,0.0693,0.0014</t>
+  </si>
+  <si>
+    <t>0.9847,0.0025,0.0048,0.0003</t>
+  </si>
+  <si>
+    <t>0.9648,0.0260,0.0078,0.0013</t>
   </si>
   <si>
     <t>0.0058,0.0025,0.9936,0.0003</t>
   </si>
   <si>
-    <t>0.8164,0.0737,0.0693,0.0016</t>
+    <t>0.8163,0.0736,0.0695,0.0016</t>
   </si>
   <si>
     <t>0.0005,0.0004,0.9994,0.0000</t>
@@ -1375,10 +1384,10 @@
     <t>0.0002,0.4250,0.9824,0.0021</t>
   </si>
   <si>
-    <t>0.0126,0.0019,0.9875,0.0015</t>
-  </si>
-  <si>
-    <t>0.0014,0.7390,0.8877,0.0005</t>
+    <t>0.0126,0.0018,0.9876,0.0015</t>
+  </si>
+  <si>
+    <t>0.0014,0.7385,0.8879,0.0005</t>
   </si>
   <si>
     <t>0.0014,0.0015,0.9981,0.0001</t>
@@ -1387,85 +1396,85 @@
     <t>0.0016,0.0001,0.9990,0.0000</t>
   </si>
   <si>
-    <t>0.0091,0.0006,0.9935,0.0002</t>
-  </si>
-  <si>
-    <t>0.0868,0.0052,0.9318,0.0023</t>
-  </si>
-  <si>
-    <t>0.1513,0.0015,0.8958,0.0008</t>
-  </si>
-  <si>
-    <t>0.4705,0.0898,0.3552,0.0114</t>
-  </si>
-  <si>
-    <t>0.0240,0.0133,0.9647,0.0032</t>
-  </si>
-  <si>
-    <t>0.0097,0.0215,0.9791,0.0005</t>
-  </si>
-  <si>
-    <t>0.0892,0.0051,0.9196,0.0035</t>
-  </si>
-  <si>
-    <t>0.1262,0.0034,0.9045,0.0020</t>
-  </si>
-  <si>
-    <t>0.4306,0.0238,0.5568,0.0042</t>
-  </si>
-  <si>
-    <t>0.5289,0.6837,0.0023,0.0001</t>
+    <t>0.0092,0.0006,0.9935,0.0002</t>
+  </si>
+  <si>
+    <t>0.0865,0.0051,0.9320,0.0023</t>
+  </si>
+  <si>
+    <t>0.1514,0.0015,0.8958,0.0008</t>
+  </si>
+  <si>
+    <t>0.4703,0.0892,0.3563,0.0114</t>
+  </si>
+  <si>
+    <t>0.0240,0.0133,0.9648,0.0032</t>
+  </si>
+  <si>
+    <t>0.0097,0.0214,0.9791,0.0005</t>
+  </si>
+  <si>
+    <t>0.0893,0.0051,0.9196,0.0035</t>
+  </si>
+  <si>
+    <t>0.1261,0.0034,0.9045,0.0020</t>
+  </si>
+  <si>
+    <t>0.4309,0.0237,0.5566,0.0042</t>
+  </si>
+  <si>
+    <t>0.5291,0.6835,0.0023,0.0001</t>
   </si>
   <si>
     <t>0.0055,0.9961,0.0044,0.0003</t>
   </si>
   <si>
-    <t>0.1013,0.9386,0.0147,0.0014</t>
-  </si>
-  <si>
-    <t>0.9415,0.0394,0.0079,0.0006</t>
-  </si>
-  <si>
-    <t>0.4212,0.6917,0.0077,0.0009</t>
-  </si>
-  <si>
-    <t>0.1676,0.8580,0.0154,0.0013</t>
-  </si>
-  <si>
-    <t>0.9445,0.0168,0.0165,0.0010</t>
-  </si>
-  <si>
-    <t>0.3910,0.0483,0.5440,0.0296</t>
-  </si>
-  <si>
-    <t>0.1627,0.0033,0.8533,0.0076</t>
-  </si>
-  <si>
-    <t>0.3047,0.0069,0.6930,0.0036</t>
+    <t>0.1014,0.9385,0.0147,0.0014</t>
+  </si>
+  <si>
+    <t>0.9414,0.0395,0.0079,0.0006</t>
+  </si>
+  <si>
+    <t>0.4211,0.6918,0.0078,0.0009</t>
+  </si>
+  <si>
+    <t>0.1680,0.8574,0.0155,0.0013</t>
+  </si>
+  <si>
+    <t>0.9444,0.0168,0.0166,0.0010</t>
+  </si>
+  <si>
+    <t>0.3911,0.0481,0.5442,0.0295</t>
+  </si>
+  <si>
+    <t>0.1628,0.0033,0.8533,0.0076</t>
+  </si>
+  <si>
+    <t>0.3040,0.0069,0.6939,0.0036</t>
   </si>
   <si>
     <t>0.0104,0.0008,0.9912,0.0006</t>
   </si>
   <si>
-    <t>0.0853,0.0053,0.9239,0.0022</t>
-  </si>
-  <si>
-    <t>0.0527,0.0196,0.9150,0.0019</t>
+    <t>0.0853,0.0052,0.9239,0.0022</t>
+  </si>
+  <si>
+    <t>0.0526,0.0195,0.9153,0.0019</t>
   </si>
   <si>
     <t>0.0051,0.0087,0.9925,0.0013</t>
   </si>
   <si>
-    <t>0.0105,0.0013,0.9928,0.0002</t>
+    <t>0.0106,0.0013,0.9928,0.0002</t>
   </si>
   <si>
     <t>0.9873,0.0015,0.0037,0.0007</t>
   </si>
   <si>
-    <t>0.9693,0.0178,0.0062,0.0025</t>
-  </si>
-  <si>
-    <t>0.9487,0.0251,0.0119,0.0043</t>
+    <t>0.9694,0.0178,0.0062,0.0025</t>
+  </si>
+  <si>
+    <t>0.9486,0.0251,0.0120,0.0043</t>
   </si>
   <si>
     <t>0.9784,0.0204,0.0025,0.0015</t>
@@ -1474,7 +1483,7 @@
     <t>0.9652,0.0207,0.0059,0.0028</t>
   </si>
   <si>
-    <t>0.9690,0.0199,0.0045,0.0022</t>
+    <t>0.9690,0.0199,0.0046,0.0022</t>
   </si>
   <si>
     <t>0.9774,0.0095,0.0040,0.0017</t>
@@ -1486,10 +1495,10 @@
     <t>0.0104,0.0007,0.9924,0.0004</t>
   </si>
   <si>
-    <t>0.0599,0.0423,0.9130,0.0019</t>
-  </si>
-  <si>
-    <t>0.2648,0.0158,0.7439,0.0126</t>
+    <t>0.0600,0.0422,0.9131,0.0019</t>
+  </si>
+  <si>
+    <t>0.2647,0.0158,0.7442,0.0126</t>
   </si>
   <si>
     <t>0.0007,0.0004,0.9993,0.0000</t>
@@ -1498,7 +1507,7 @@
     <t>0.0002,0.0049,0.9990,0.0004</t>
   </si>
   <si>
-    <t>0.0076,0.1298,0.9612,0.0009</t>
+    <t>0.0076,0.1292,0.9613,0.0009</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9999,0.0000</t>
@@ -1513,13 +1522,13 @@
     <t>0.0040,0.0149,0.9915,0.0012</t>
   </si>
   <si>
-    <t>0.0347,0.0304,0.9393,0.0051</t>
-  </si>
-  <si>
-    <t>0.7226,0.0035,0.2892,0.0028</t>
-  </si>
-  <si>
-    <t>0.7851,0.0010,0.2125,0.0019</t>
+    <t>0.0347,0.0303,0.9394,0.0051</t>
+  </si>
+  <si>
+    <t>0.7226,0.0035,0.2893,0.0028</t>
+  </si>
+  <si>
+    <t>0.7846,0.0010,0.2132,0.0019</t>
   </si>
   <si>
     <t>0.9477,0.0075,0.0251,0.0003</t>
@@ -1534,13 +1543,13 @@
     <t>0.9800,0.0111,0.0031,0.0011</t>
   </si>
   <si>
-    <t>0.9117,0.0654,0.0127,0.0014</t>
+    <t>0.9116,0.0654,0.0128,0.0014</t>
   </si>
   <si>
     <t>0.9871,0.0027,0.0028,0.0006</t>
   </si>
   <si>
-    <t>0.9598,0.0393,0.0030,0.0010</t>
+    <t>0.9597,0.0393,0.0031,0.0010</t>
   </si>
   <si>
     <t>0.9838,0.0088,0.0032,0.0009</t>
@@ -1549,7 +1558,7 @@
     <t>0.9685,0.0098,0.0075,0.0022</t>
   </si>
   <si>
-    <t>0.0073,0.0799,0.9588,0.0014</t>
+    <t>0.0073,0.0796,0.9588,0.0014</t>
   </si>
   <si>
     <t>0.0015,0.0130,0.9972,0.0002</t>
@@ -1558,16 +1567,16 @@
     <t>0.0031,0.0048,0.9957,0.0002</t>
   </si>
   <si>
-    <t>0.0184,0.0736,0.9340,0.0011</t>
+    <t>0.0185,0.0732,0.9343,0.0011</t>
   </si>
   <si>
     <t>0.0134,0.0007,0.9919,0.0003</t>
   </si>
   <si>
-    <t>0.6187,0.0144,0.0956,0.0516</t>
-  </si>
-  <si>
-    <t>0.1259,0.0050,0.8993,0.0059</t>
+    <t>0.6183,0.0144,0.0960,0.0517</t>
+  </si>
+  <si>
+    <t>0.1257,0.0050,0.8995,0.0059</t>
   </si>
   <si>
     <t>0.0008,0.0010,0.9977,0.0019</t>
@@ -1579,7 +1588,7 @@
     <t>0.0003,0.0044,0.0003,0.9998</t>
   </si>
   <si>
-    <t>0.0356,0.0003,0.0008,0.9917</t>
+    <t>0.0355,0.0003,0.0008,0.9917</t>
   </si>
   <si>
     <t>0.0001,0.0002,0.0266,0.9998</t>
@@ -1588,7 +1597,7 @@
     <t>0.0001,0.0006,0.0012,0.9999</t>
   </si>
   <si>
-    <t>0.6077,0.0100,0.0115,0.2535</t>
+    <t>0.6079,0.0099,0.0116,0.2534</t>
   </si>
 </sst>
 </file>
@@ -1974,7 +1983,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1988,7 +1997,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2002,7 +2011,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2016,7 +2025,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2030,7 +2039,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2044,7 +2053,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2058,7 +2067,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2072,7 +2081,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2086,7 +2095,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2100,7 +2109,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2114,7 +2123,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2128,7 +2137,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2142,7 +2151,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2156,7 +2165,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2170,7 +2179,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2184,7 +2193,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2198,7 +2207,7 @@
         <v>266</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2212,7 +2221,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2226,7 +2235,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2240,7 +2249,7 @@
         <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2254,7 +2263,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2268,7 +2277,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2279,10 +2288,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2296,7 +2305,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2310,7 +2319,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2324,7 +2333,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2338,7 +2347,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2352,7 +2361,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2366,7 +2375,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2380,7 +2389,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2394,7 +2403,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2408,7 +2417,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2422,7 +2431,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2436,7 +2445,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2450,7 +2459,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2464,7 +2473,7 @@
         <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2478,7 +2487,7 @@
         <v>267</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2489,10 +2498,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2506,7 +2515,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2520,7 +2529,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2534,7 +2543,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2545,10 +2554,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2562,7 +2571,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2576,7 +2585,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2587,10 +2596,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2604,7 +2613,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2618,7 +2627,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2632,7 +2641,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2646,7 +2655,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2660,7 +2669,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2674,7 +2683,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2688,7 +2697,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2702,7 +2711,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2716,7 +2725,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2730,7 +2739,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2744,7 +2753,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2758,7 +2767,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2772,7 +2781,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2786,7 +2795,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2800,7 +2809,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2814,7 +2823,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2825,10 +2834,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2842,7 +2851,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2856,7 +2865,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2867,10 +2876,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2884,7 +2893,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2898,7 +2907,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2912,7 +2921,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2926,7 +2935,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2940,7 +2949,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2954,7 +2963,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2965,10 +2974,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2979,10 +2988,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2996,7 +3005,7 @@
         <v>267</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3007,10 +3016,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3024,7 +3033,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3038,7 +3047,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3052,7 +3061,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3066,7 +3075,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3080,7 +3089,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3094,7 +3103,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3105,10 +3114,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3119,10 +3128,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3133,10 +3142,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3147,10 +3156,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3161,10 +3170,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3178,7 +3187,7 @@
         <v>267</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3192,7 +3201,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3206,7 +3215,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3220,7 +3229,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3234,7 +3243,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3248,7 +3257,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3262,7 +3271,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3276,7 +3285,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3290,7 +3299,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3304,7 +3313,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3318,7 +3327,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3332,7 +3341,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3346,7 +3355,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3360,7 +3369,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3374,7 +3383,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3388,7 +3397,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3402,7 +3411,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3416,7 +3425,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3430,7 +3439,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3444,7 +3453,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3458,7 +3467,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3472,7 +3481,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3486,7 +3495,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3497,10 +3506,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3514,7 +3523,7 @@
         <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3528,7 +3537,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3542,7 +3551,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3556,7 +3565,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3570,7 +3579,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3584,7 +3593,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3598,7 +3607,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3612,7 +3621,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3623,10 +3632,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D120" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3640,7 +3649,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3654,7 +3663,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3668,7 +3677,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3682,7 +3691,7 @@
         <v>267</v>
       </c>
       <c r="D124" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3696,7 +3705,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3710,7 +3719,7 @@
         <v>267</v>
       </c>
       <c r="D126" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3724,7 +3733,7 @@
         <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3738,7 +3747,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3752,7 +3761,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3766,7 +3775,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3780,7 +3789,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3794,7 +3803,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3808,7 +3817,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3822,7 +3831,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3836,7 +3845,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3847,10 +3856,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D136" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3861,10 +3870,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D137" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3878,7 +3887,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3892,7 +3901,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3906,7 +3915,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3917,10 +3926,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D141" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3934,7 +3943,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3948,7 +3957,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3962,7 +3971,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3976,7 +3985,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3990,7 +3999,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4004,7 +4013,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4015,10 +4024,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4032,7 +4041,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4046,7 +4055,7 @@
         <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4060,7 +4069,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4074,7 +4083,7 @@
         <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4088,7 +4097,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4102,7 +4111,7 @@
         <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4116,7 +4125,7 @@
         <v>266</v>
       </c>
       <c r="D155" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4130,7 +4139,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4144,7 +4153,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4158,7 +4167,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4172,7 +4181,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4186,7 +4195,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4200,7 +4209,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4214,7 +4223,7 @@
         <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4228,7 +4237,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4242,7 +4251,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4256,7 +4265,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4270,7 +4279,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4284,7 +4293,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4298,7 +4307,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4312,7 +4321,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4326,7 +4335,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4340,7 +4349,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4354,7 +4363,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4368,7 +4377,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4382,7 +4391,7 @@
         <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4396,7 +4405,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4410,7 +4419,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4424,7 +4433,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4438,7 +4447,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4452,7 +4461,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4466,7 +4475,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4480,7 +4489,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4494,7 +4503,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4508,7 +4517,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4522,7 +4531,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4536,7 +4545,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4547,10 +4556,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D186" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4564,7 +4573,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4578,7 +4587,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4592,7 +4601,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4606,7 +4615,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4620,7 +4629,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4631,10 +4640,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D192" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4648,7 +4657,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4662,7 +4671,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4676,7 +4685,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4690,7 +4699,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4704,7 +4713,7 @@
         <v>266</v>
       </c>
       <c r="D197" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4715,10 +4724,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D198" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4732,7 +4741,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4746,7 +4755,7 @@
         <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4760,7 +4769,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4774,7 +4783,7 @@
         <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4788,7 +4797,7 @@
         <v>267</v>
       </c>
       <c r="D203" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4802,7 +4811,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4816,7 +4825,7 @@
         <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4830,7 +4839,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4844,7 +4853,7 @@
         <v>266</v>
       </c>
       <c r="D207" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4858,7 +4867,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4872,7 +4881,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4886,7 +4895,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4900,7 +4909,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4914,7 +4923,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4928,7 +4937,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4942,7 +4951,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4956,7 +4965,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4970,7 +4979,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4984,7 +4993,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4998,7 +5007,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5012,7 +5021,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5026,7 +5035,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5040,7 +5049,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5054,7 +5063,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5068,7 +5077,7 @@
         <v>266</v>
       </c>
       <c r="D223" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5082,7 +5091,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5096,7 +5105,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5110,7 +5119,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5124,7 +5133,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5138,7 +5147,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5152,7 +5161,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5166,7 +5175,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5180,7 +5189,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5194,7 +5203,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5208,7 +5217,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5222,7 +5231,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5236,7 +5245,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5250,7 +5259,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5264,7 +5273,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5278,7 +5287,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5292,7 +5301,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5306,7 +5315,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5320,7 +5329,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5334,7 +5343,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5348,7 +5357,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5362,7 +5371,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5376,7 +5385,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5390,7 +5399,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5404,7 +5413,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5418,7 +5427,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5432,7 +5441,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5446,7 +5455,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5460,7 +5469,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5474,7 +5483,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5488,7 +5497,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5502,7 +5511,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5516,7 +5525,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5530,7 +5539,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
